--- a/assessment_forms/029_high_school_student_skills_assessment_questionnaire--assessment_forms.xlsx
+++ b/assessment_forms/029_high_school_student_skills_assessment_questionnaire--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'algebra'}</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'Algebra'}</t>
+          <t>Algebra</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'calculus'}</t>
+          <t>calculus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'Calculus'}</t>
+          <t>Calculus</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'geometry'}</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'Geometry'}</t>
+          <t>Geometry</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'d',_'label':_'trigonometry'}</t>
+          <t>trigonometry</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'd', 'label': 'Trigonometry'}</t>
+          <t>Trigonometry</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'e',_'label':_'statistics'}</t>
+          <t>statistics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'e', 'label': 'Statistics'}</t>
+          <t>Statistics</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'business/entrepreneurship'}</t>
+          <t>business/entrepreneurship</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'Business/Entrepreneurship'}</t>
+          <t>Business/Entrepreneurship</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'art/design'}</t>
+          <t>art/design</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'Art/Design'}</t>
+          <t>Art/Design</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'d',_'label':_'social_science'}</t>
+          <t>social_science</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'd', 'label': 'Social Science'}</t>
+          <t>Social Science</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'e',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'e', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a',_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'a', 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b',_'label':_'currently_in_high_school'}</t>
+          <t>currently_in_high_school</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'b', 'label': 'Currently in high school'}</t>
+          <t>Currently in high school</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c',_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'c', 'label': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'d',_'label':_'associates'}</t>
+          <t>associates</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'd', 'label': 'Associates'}</t>
+          <t>Associates</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'e',_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'e', 'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'f',_'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'f', 'label': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'g',_'label':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'g', 'label': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
